--- a/Dashboard_GIS/ข้อมูลดิบ/แรงดันน้ำ/PRESSURE_สระแก้ว_ปีงบ69.xlsx
+++ b/Dashboard_GIS/ข้อมูลดิบ/แรงดันน้ำ/PRESSURE_สระแก้ว_ปีงบ69.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Report" sheetId="1" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" name="__bookmark_1" vbProcedure="false">Report!$A$4:$M$56</definedName>
+    <definedName function="false" hidden="false" name="__bookmark_1" vbProcedure="false">Report!$A$4:$N$56</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="73">
   <si>
     <t xml:space="preserve">รายงานการตรวจวัดค่าแรงดันน้ำ</t>
   </si>
@@ -322,6 +322,48 @@
         <family val="2"/>
         <charset val="222"/>
       </rPr>
+      <t xml:space="preserve">เม</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t xml:space="preserve">ย</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t xml:space="preserve">. 69</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
       <t xml:space="preserve">ก</t>
     </r>
     <r>
@@ -1210,7 +1252,7 @@
     <t xml:space="preserve">พิมพ์รายงานวันที่</t>
   </si>
   <si>
-    <t xml:space="preserve">4/3/2569</t>
+    <t xml:space="preserve">3/4/2569</t>
   </si>
   <si>
     <t xml:space="preserve">หน้าที่</t>
@@ -1423,7 +1465,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:V61"/>
+  <dimension ref="A1:W61"/>
   <sheetFormatPr defaultColWidth="11.74609375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4.6"/>
@@ -1437,15 +1479,16 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="3.33"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="6.6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="6.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="23.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="9.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="1.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="7.03"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="1.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="5.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="0.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="2.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="6.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="17.02"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="9.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="1.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="5.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="7.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="1.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="5.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="0.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="2.7"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1467,11 +1510,12 @@
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
-      <c r="Q1" s="3"/>
+      <c r="Q1" s="2"/>
       <c r="R1" s="3"/>
       <c r="S1" s="3"/>
       <c r="T1" s="3"/>
       <c r="U1" s="3"/>
+      <c r="V1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1"/>
@@ -1492,11 +1536,12 @@
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
       <c r="P2" s="2"/>
-      <c r="Q2" s="3"/>
+      <c r="Q2" s="2"/>
       <c r="R2" s="3"/>
       <c r="S2" s="3"/>
       <c r="T2" s="3"/>
       <c r="U2" s="3"/>
+      <c r="V2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1"/>
@@ -1517,11 +1562,12 @@
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
-      <c r="Q3" s="3"/>
+      <c r="Q3" s="2"/>
       <c r="R3" s="3"/>
       <c r="S3" s="3"/>
       <c r="T3" s="3"/>
       <c r="U3" s="3"/>
+      <c r="V3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4"/>
@@ -1537,6 +1583,7 @@
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
@@ -1571,6 +1618,9 @@
       </c>
       <c r="M5" s="5" t="s">
         <v>12</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1587,13 +1637,14 @@
       <c r="K6" s="6"/>
       <c r="L6" s="6"/>
       <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="n">
         <v>1</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
@@ -1617,9 +1668,12 @@
       </c>
       <c r="K7" s="9"/>
       <c r="L7" s="9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1628,7 +1682,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
@@ -1652,9 +1706,12 @@
       </c>
       <c r="K8" s="9"/>
       <c r="L8" s="9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1663,7 +1720,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
@@ -1687,9 +1744,12 @@
       </c>
       <c r="K9" s="9"/>
       <c r="L9" s="9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1698,12 +1758,12 @@
         <v>4</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
       <c r="E10" s="7" t="n">
-        <v>1.78</v>
+        <v>1.783333</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>1.8</v>
@@ -1722,9 +1782,12 @@
       </c>
       <c r="K10" s="9"/>
       <c r="L10" s="9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1733,12 +1796,12 @@
         <v>5</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
       <c r="E11" s="7" t="n">
-        <v>1.48</v>
+        <v>1.483333</v>
       </c>
       <c r="F11" s="9" t="n">
         <v>1.4</v>
@@ -1757,9 +1820,12 @@
       </c>
       <c r="K11" s="9"/>
       <c r="L11" s="9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1768,7 +1834,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
@@ -1792,9 +1858,12 @@
       </c>
       <c r="K12" s="9"/>
       <c r="L12" s="9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1803,12 +1872,12 @@
         <v>7</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
       <c r="E13" s="7" t="n">
-        <v>1.36</v>
+        <v>1.366666</v>
       </c>
       <c r="F13" s="9" t="n">
         <v>1.4</v>
@@ -1827,9 +1896,12 @@
       </c>
       <c r="K13" s="9"/>
       <c r="L13" s="9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1838,7 +1910,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
@@ -1862,9 +1934,12 @@
       </c>
       <c r="K14" s="9"/>
       <c r="L14" s="9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1873,7 +1948,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
@@ -1897,9 +1972,12 @@
       </c>
       <c r="K15" s="9"/>
       <c r="L15" s="9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1908,12 +1986,12 @@
         <v>10</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="7" t="n">
-        <v>1.48</v>
+        <v>1.483333</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>1.4</v>
@@ -1932,9 +2010,12 @@
       </c>
       <c r="K16" s="9"/>
       <c r="L16" s="9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1943,7 +2024,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
@@ -1967,9 +2048,12 @@
       </c>
       <c r="K17" s="9"/>
       <c r="L17" s="9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1978,7 +2062,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
@@ -2002,9 +2086,12 @@
       </c>
       <c r="K18" s="9"/>
       <c r="L18" s="9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2013,7 +2100,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C19" s="8"/>
       <c r="D19" s="8"/>
@@ -2037,9 +2124,12 @@
       </c>
       <c r="K19" s="9"/>
       <c r="L19" s="9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2048,7 +2138,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20" s="8"/>
       <c r="D20" s="8"/>
@@ -2072,9 +2162,12 @@
       </c>
       <c r="K20" s="9"/>
       <c r="L20" s="9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2083,12 +2176,12 @@
         <v>15</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="7" t="n">
-        <v>1.28</v>
+        <v>1.283333</v>
       </c>
       <c r="F21" s="9" t="n">
         <v>1.2</v>
@@ -2107,9 +2200,12 @@
       </c>
       <c r="K21" s="9"/>
       <c r="L21" s="9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2118,12 +2214,12 @@
         <v>16</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="7" t="n">
-        <v>1.48</v>
+        <v>1.483333</v>
       </c>
       <c r="F22" s="9" t="n">
         <v>1.4</v>
@@ -2142,9 +2238,12 @@
       </c>
       <c r="K22" s="9"/>
       <c r="L22" s="9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2153,7 +2252,7 @@
         <v>17</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
@@ -2177,9 +2276,12 @@
       </c>
       <c r="K23" s="9"/>
       <c r="L23" s="9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2188,7 +2290,7 @@
         <v>18</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
@@ -2212,9 +2314,12 @@
       </c>
       <c r="K24" s="9"/>
       <c r="L24" s="9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2223,7 +2328,7 @@
         <v>19</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
@@ -2247,9 +2352,12 @@
       </c>
       <c r="K25" s="9"/>
       <c r="L25" s="9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M25" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2258,7 +2366,7 @@
         <v>20</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
@@ -2282,9 +2390,12 @@
       </c>
       <c r="K26" s="9"/>
       <c r="L26" s="9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M26" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2293,12 +2404,12 @@
         <v>21</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="7" t="n">
-        <v>1.48</v>
+        <v>1.483333</v>
       </c>
       <c r="F27" s="9" t="n">
         <v>1.5</v>
@@ -2317,9 +2428,12 @@
       </c>
       <c r="K27" s="9"/>
       <c r="L27" s="9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M27" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2328,7 +2442,7 @@
         <v>22</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
@@ -2352,9 +2466,12 @@
       </c>
       <c r="K28" s="9"/>
       <c r="L28" s="9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M28" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2363,7 +2480,7 @@
         <v>23</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C29" s="8"/>
       <c r="D29" s="8"/>
@@ -2387,9 +2504,12 @@
       </c>
       <c r="K29" s="9"/>
       <c r="L29" s="9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M29" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2398,7 +2518,7 @@
         <v>24</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
@@ -2422,9 +2542,12 @@
       </c>
       <c r="K30" s="9"/>
       <c r="L30" s="9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M30" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2433,7 +2556,7 @@
         <v>25</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
@@ -2457,9 +2580,12 @@
       </c>
       <c r="K31" s="9"/>
       <c r="L31" s="9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2468,12 +2594,12 @@
         <v>26</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
       <c r="E32" s="7" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="F32" s="9" t="n">
         <v>1.4</v>
@@ -2492,9 +2618,12 @@
       </c>
       <c r="K32" s="9"/>
       <c r="L32" s="9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2503,7 +2632,7 @@
         <v>27</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
@@ -2527,9 +2656,12 @@
       </c>
       <c r="K33" s="9"/>
       <c r="L33" s="9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2538,7 +2670,7 @@
         <v>28</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C34" s="8"/>
       <c r="D34" s="8"/>
@@ -2562,9 +2694,12 @@
       </c>
       <c r="K34" s="9"/>
       <c r="L34" s="9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M34" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2573,12 +2708,12 @@
         <v>29</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C35" s="8"/>
       <c r="D35" s="8"/>
       <c r="E35" s="7" t="n">
-        <v>2.16</v>
+        <v>2.166666</v>
       </c>
       <c r="F35" s="9" t="n">
         <v>2.2</v>
@@ -2597,9 +2732,12 @@
       </c>
       <c r="K35" s="9"/>
       <c r="L35" s="9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M35" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2608,7 +2746,7 @@
         <v>30</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C36" s="8"/>
       <c r="D36" s="8"/>
@@ -2632,9 +2770,12 @@
       </c>
       <c r="K36" s="9"/>
       <c r="L36" s="9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M36" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2643,12 +2784,12 @@
         <v>31</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C37" s="8"/>
       <c r="D37" s="8"/>
       <c r="E37" s="7" t="n">
-        <v>1.22</v>
+        <v>1.233333</v>
       </c>
       <c r="F37" s="9" t="n">
         <v>1.2</v>
@@ -2667,9 +2808,12 @@
       </c>
       <c r="K37" s="9"/>
       <c r="L37" s="9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M37" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2678,7 +2822,7 @@
         <v>32</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C38" s="8"/>
       <c r="D38" s="8"/>
@@ -2702,9 +2846,12 @@
       </c>
       <c r="K38" s="9"/>
       <c r="L38" s="9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M38" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2713,7 +2860,7 @@
         <v>33</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C39" s="8"/>
       <c r="D39" s="8"/>
@@ -2737,9 +2884,12 @@
       </c>
       <c r="K39" s="9"/>
       <c r="L39" s="9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M39" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2748,12 +2898,12 @@
         <v>34</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C40" s="8"/>
       <c r="D40" s="8"/>
       <c r="E40" s="7" t="n">
-        <v>1.3</v>
+        <v>1.316666</v>
       </c>
       <c r="F40" s="9" t="n">
         <v>1.3</v>
@@ -2772,9 +2922,12 @@
       </c>
       <c r="K40" s="9"/>
       <c r="L40" s="9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M40" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2783,7 +2936,7 @@
         <v>35</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C41" s="8"/>
       <c r="D41" s="8"/>
@@ -2807,9 +2960,12 @@
       </c>
       <c r="K41" s="9"/>
       <c r="L41" s="9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M41" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2818,7 +2974,7 @@
         <v>36</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C42" s="8"/>
       <c r="D42" s="8"/>
@@ -2842,9 +2998,12 @@
       </c>
       <c r="K42" s="9"/>
       <c r="L42" s="9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M42" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2853,12 +3012,12 @@
         <v>37</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
       <c r="E43" s="7" t="n">
-        <v>1.78</v>
+        <v>1.783333</v>
       </c>
       <c r="F43" s="9" t="n">
         <v>1.8</v>
@@ -2877,9 +3036,12 @@
       </c>
       <c r="K43" s="9"/>
       <c r="L43" s="9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M43" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2888,12 +3050,12 @@
         <v>38</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C44" s="8"/>
       <c r="D44" s="8"/>
       <c r="E44" s="7" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="F44" s="9" t="n">
         <v>1.8</v>
@@ -2912,9 +3074,12 @@
       </c>
       <c r="K44" s="9"/>
       <c r="L44" s="9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M44" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2923,7 +3088,7 @@
         <v>39</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C45" s="8"/>
       <c r="D45" s="8"/>
@@ -2947,9 +3112,12 @@
       </c>
       <c r="K45" s="9"/>
       <c r="L45" s="9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M45" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2958,7 +3126,7 @@
         <v>40</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C46" s="8"/>
       <c r="D46" s="8"/>
@@ -2982,9 +3150,12 @@
       </c>
       <c r="K46" s="9"/>
       <c r="L46" s="9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M46" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2993,7 +3164,7 @@
         <v>41</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C47" s="8"/>
       <c r="D47" s="8"/>
@@ -3017,9 +3188,12 @@
       </c>
       <c r="K47" s="9"/>
       <c r="L47" s="9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M47" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3028,12 +3202,12 @@
         <v>42</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C48" s="8"/>
       <c r="D48" s="8"/>
       <c r="E48" s="7" t="n">
-        <v>2.16</v>
+        <v>2.166666</v>
       </c>
       <c r="F48" s="9" t="n">
         <v>2.2</v>
@@ -3052,9 +3226,12 @@
       </c>
       <c r="K48" s="9"/>
       <c r="L48" s="9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M48" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3063,12 +3240,12 @@
         <v>43</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C49" s="8"/>
       <c r="D49" s="8"/>
       <c r="E49" s="7" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="F49" s="9" t="n">
         <v>2.2</v>
@@ -3087,9 +3264,12 @@
       </c>
       <c r="K49" s="9"/>
       <c r="L49" s="9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M49" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3098,12 +3278,12 @@
         <v>44</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C50" s="8"/>
       <c r="D50" s="8"/>
       <c r="E50" s="7" t="n">
-        <v>2.16</v>
+        <v>2.166666</v>
       </c>
       <c r="F50" s="9" t="n">
         <v>2.2</v>
@@ -3122,9 +3302,12 @@
       </c>
       <c r="K50" s="9"/>
       <c r="L50" s="9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M50" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3133,7 +3316,7 @@
         <v>45</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C51" s="8"/>
       <c r="D51" s="8"/>
@@ -3157,9 +3340,12 @@
       </c>
       <c r="K51" s="9"/>
       <c r="L51" s="9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M51" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3168,7 +3354,7 @@
         <v>46</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C52" s="8"/>
       <c r="D52" s="8"/>
@@ -3192,9 +3378,12 @@
       </c>
       <c r="K52" s="9"/>
       <c r="L52" s="9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M52" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3203,7 +3392,7 @@
         <v>47</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C53" s="8"/>
       <c r="D53" s="8"/>
@@ -3227,9 +3416,12 @@
       </c>
       <c r="K53" s="9"/>
       <c r="L53" s="9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M53" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3238,7 +3430,7 @@
         <v>48</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C54" s="8"/>
       <c r="D54" s="8"/>
@@ -3262,9 +3454,12 @@
       </c>
       <c r="K54" s="9"/>
       <c r="L54" s="9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M54" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3273,7 +3468,7 @@
         <v>49</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C55" s="8"/>
       <c r="D55" s="8"/>
@@ -3297,9 +3492,12 @@
       </c>
       <c r="K55" s="9"/>
       <c r="L55" s="9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M55" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3308,7 +3506,7 @@
         <v>50</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C56" s="8"/>
       <c r="D56" s="8"/>
@@ -3332,9 +3530,12 @@
       </c>
       <c r="K56" s="9"/>
       <c r="L56" s="9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M56" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3361,10 +3562,11 @@
       <c r="T57" s="10"/>
       <c r="U57" s="10"/>
       <c r="V57" s="10"/>
+      <c r="W57" s="10"/>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B58" s="11"/>
       <c r="C58" s="11"/>
@@ -3376,7 +3578,7 @@
       <c r="I58" s="11"/>
       <c r="J58" s="11"/>
       <c r="K58" s="11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L58" s="11"/>
       <c r="M58" s="11"/>
@@ -3389,10 +3591,11 @@
       <c r="T58" s="11"/>
       <c r="U58" s="11"/>
       <c r="V58" s="11"/>
+      <c r="W58" s="11"/>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B59" s="11"/>
       <c r="C59" s="11"/>
@@ -3404,7 +3607,7 @@
       <c r="I59" s="11"/>
       <c r="J59" s="11"/>
       <c r="K59" s="11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L59" s="11"/>
       <c r="M59" s="11"/>
@@ -3417,10 +3620,11 @@
       <c r="T59" s="11"/>
       <c r="U59" s="11"/>
       <c r="V59" s="11"/>
+      <c r="W59" s="11"/>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B60" s="12"/>
       <c r="C60" s="12"/>
@@ -3432,7 +3636,7 @@
       <c r="I60" s="12"/>
       <c r="J60" s="12"/>
       <c r="K60" s="12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="L60" s="12"/>
       <c r="M60" s="12"/>
@@ -3445,6 +3649,7 @@
       <c r="T60" s="12"/>
       <c r="U60" s="12"/>
       <c r="V60" s="12"/>
+      <c r="W60" s="12"/>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="13"/>
@@ -3458,39 +3663,40 @@
       <c r="I61" s="10"/>
       <c r="J61" s="10"/>
       <c r="K61" s="13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L61" s="13"/>
       <c r="M61" s="13"/>
       <c r="N61" s="13"/>
-      <c r="O61" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="P61" s="13" t="s">
+      <c r="O61" s="13"/>
+      <c r="P61" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="Q61" s="13"/>
-      <c r="R61" s="15" t="s">
+      <c r="Q61" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="S61" s="12" t="s">
+      <c r="R61" s="13"/>
+      <c r="S61" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="T61" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="U61" s="10"/>
+      <c r="T61" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="U61" s="14" t="s">
+        <v>71</v>
+      </c>
       <c r="V61" s="10"/>
+      <c r="W61" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="126">
     <mergeCell ref="A1:B3"/>
-    <mergeCell ref="C1:P1"/>
-    <mergeCell ref="Q1:U1"/>
-    <mergeCell ref="C2:P2"/>
-    <mergeCell ref="Q2:U2"/>
-    <mergeCell ref="C3:P3"/>
-    <mergeCell ref="Q3:U3"/>
+    <mergeCell ref="C1:Q1"/>
+    <mergeCell ref="R1:V1"/>
+    <mergeCell ref="C2:Q2"/>
+    <mergeCell ref="R2:V2"/>
+    <mergeCell ref="C3:Q3"/>
+    <mergeCell ref="R3:V3"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="J4:K4"/>
     <mergeCell ref="B5:D5"/>
@@ -3598,18 +3804,18 @@
     <mergeCell ref="B56:D56"/>
     <mergeCell ref="J56:K56"/>
     <mergeCell ref="A57:J57"/>
-    <mergeCell ref="K57:V57"/>
+    <mergeCell ref="K57:W57"/>
     <mergeCell ref="A58:J58"/>
-    <mergeCell ref="K58:V58"/>
+    <mergeCell ref="K58:W58"/>
     <mergeCell ref="A59:J59"/>
-    <mergeCell ref="K59:V59"/>
+    <mergeCell ref="K59:W59"/>
     <mergeCell ref="A60:J60"/>
-    <mergeCell ref="K60:V60"/>
+    <mergeCell ref="K60:W60"/>
     <mergeCell ref="A61:C61"/>
     <mergeCell ref="D61:J61"/>
-    <mergeCell ref="K61:N61"/>
-    <mergeCell ref="P61:Q61"/>
-    <mergeCell ref="U61:V61"/>
+    <mergeCell ref="K61:O61"/>
+    <mergeCell ref="Q61:R61"/>
+    <mergeCell ref="V61:W61"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
